--- a/results/supplementary/tables_submission/TableS6_geo_ARG_burden_by_country.xlsx
+++ b/results/supplementary/tables_submission/TableS6_geo_ARG_burden_by_country.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="TableS6_geo_ARG_burden_by_count" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -73,9 +73,7 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -443,53 +441,53 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR39"/>
+  <dimension ref="A1:AR38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="18" customWidth="1" min="21" max="21"/>
-    <col width="17" customWidth="1" min="22" max="22"/>
-    <col width="17" customWidth="1" min="23" max="23"/>
-    <col width="17" customWidth="1" min="24" max="24"/>
-    <col width="10" customWidth="1" min="25" max="25"/>
-    <col width="10" customWidth="1" min="26" max="26"/>
-    <col width="10" customWidth="1" min="27" max="27"/>
-    <col width="10" customWidth="1" min="28" max="28"/>
-    <col width="10" customWidth="1" min="29" max="29"/>
-    <col width="10" customWidth="1" min="30" max="30"/>
-    <col width="11" customWidth="1" min="31" max="31"/>
-    <col width="11" customWidth="1" min="32" max="32"/>
-    <col width="10" customWidth="1" min="33" max="33"/>
-    <col width="10" customWidth="1" min="34" max="34"/>
-    <col width="10" customWidth="1" min="35" max="35"/>
-    <col width="10" customWidth="1" min="36" max="36"/>
-    <col width="10" customWidth="1" min="37" max="37"/>
-    <col width="10" customWidth="1" min="38" max="38"/>
-    <col width="13" customWidth="1" min="39" max="39"/>
-    <col width="10" customWidth="1" min="40" max="40"/>
-    <col width="10" customWidth="1" min="41" max="41"/>
-    <col width="10" customWidth="1" min="42" max="42"/>
-    <col width="11" customWidth="1" min="43" max="43"/>
-    <col width="11" customWidth="1" min="44" max="44"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="23" max="23"/>
+    <col width="15" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="9" customWidth="1" min="31" max="31"/>
+    <col width="9" customWidth="1" min="32" max="32"/>
+    <col width="8" customWidth="1" min="33" max="33"/>
+    <col width="8" customWidth="1" min="34" max="34"/>
+    <col width="8" customWidth="1" min="35" max="35"/>
+    <col width="8" customWidth="1" min="36" max="36"/>
+    <col width="8" customWidth="1" min="37" max="37"/>
+    <col width="8" customWidth="1" min="38" max="38"/>
+    <col width="11" customWidth="1" min="39" max="39"/>
+    <col width="8" customWidth="1" min="40" max="40"/>
+    <col width="8" customWidth="1" min="41" max="41"/>
+    <col width="8" customWidth="1" min="42" max="42"/>
+    <col width="9" customWidth="1" min="43" max="43"/>
+    <col width="9" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -742,7 +740,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>0.6140</t>
+          <t>0.614</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -782,17 +780,17 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -802,22 +800,22 @@
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
@@ -832,7 +830,7 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
@@ -842,12 +840,12 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0.6140</t>
+          <t>0.614</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
@@ -867,7 +865,7 @@
       </c>
       <c r="AE2" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF2" s="2" t="inlineStr">
@@ -912,7 +910,7 @@
       </c>
       <c r="AN2" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO2" s="2" t="inlineStr">
@@ -927,7 +925,7 @@
       </c>
       <c r="AQ2" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AR2" s="2" t="inlineStr">
@@ -959,7 +957,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>0.2500</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -1004,7 +1002,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -1014,17 +1012,17 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr">
@@ -1034,12 +1032,12 @@
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="V3" s="3" t="inlineStr">
@@ -1049,7 +1047,7 @@
       </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X3" s="3" t="inlineStr">
@@ -1064,7 +1062,7 @@
       </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA3" s="3" t="inlineStr">
@@ -1074,7 +1072,7 @@
       </c>
       <c r="AB3" s="3" t="inlineStr">
         <is>
-          <t>0.3750</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="AC3" s="3" t="inlineStr">
@@ -1084,12 +1082,12 @@
       </c>
       <c r="AD3" s="3" t="inlineStr">
         <is>
-          <t>1.0000</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AE3" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF3" s="3" t="inlineStr">
@@ -1124,7 +1122,7 @@
       </c>
       <c r="AL3" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AM3" s="3" t="inlineStr">
@@ -1134,7 +1132,7 @@
       </c>
       <c r="AN3" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO3" s="3" t="inlineStr">
@@ -1149,12 +1147,12 @@
       </c>
       <c r="AQ3" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1224,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -1241,12 +1239,12 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -1256,12 +1254,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -1271,7 +1269,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
@@ -1286,12 +1284,12 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -1301,7 +1299,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>0.1910</t>
+          <t>0.191</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
@@ -1311,7 +1309,7 @@
       </c>
       <c r="AE4" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF4" s="2" t="inlineStr">
@@ -1356,7 +1354,7 @@
       </c>
       <c r="AN4" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO4" s="2" t="inlineStr">
@@ -1371,12 +1369,12 @@
       </c>
       <c r="AQ4" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AR4" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1406,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>0.5000</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1448,42 +1446,42 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>0.1010</t>
+          <t>0.101</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
@@ -1508,7 +1506,7 @@
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1533,7 +1531,7 @@
       </c>
       <c r="AE5" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF5" s="3" t="inlineStr">
@@ -1553,7 +1551,7 @@
       </c>
       <c r="AI5" s="3" t="inlineStr">
         <is>
-          <t>0.5960</t>
+          <t>0.596</t>
         </is>
       </c>
       <c r="AJ5" s="3" t="inlineStr">
@@ -1593,12 +1591,12 @@
       </c>
       <c r="AQ5" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1633,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1.0000</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1645,7 +1643,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1670,27 +1668,27 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1700,12 +1698,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1725,12 +1723,12 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>0.6370</t>
+          <t>0.637</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1740,7 +1738,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1755,7 +1753,7 @@
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF6" s="2" t="inlineStr">
@@ -1790,7 +1788,7 @@
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AM6" s="2" t="inlineStr">
@@ -1815,12 +1813,12 @@
       </c>
       <c r="AQ6" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AR6" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1855,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>1.0000</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -1892,27 +1890,27 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
@@ -1922,12 +1920,12 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
@@ -1952,12 +1950,12 @@
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AB7" s="3" t="inlineStr">
@@ -1972,12 +1970,12 @@
       </c>
       <c r="AD7" s="3" t="inlineStr">
         <is>
-          <t>1.0000</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AE7" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF7" s="3" t="inlineStr">
@@ -2022,7 +2020,7 @@
       </c>
       <c r="AN7" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO7" s="3" t="inlineStr">
@@ -2037,12 +2035,12 @@
       </c>
       <c r="AQ7" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2057,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>13.0510</t>
+          <t>13.051</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2079,7 +2077,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0.9490</t>
+          <t>0.949</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -2114,7 +2112,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -2129,12 +2127,12 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -2144,12 +2142,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -2174,7 +2172,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -2199,7 +2197,7 @@
       </c>
       <c r="AE8" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF8" s="2" t="inlineStr">
@@ -2239,7 +2237,7 @@
       </c>
       <c r="AM8" s="2" t="inlineStr">
         <is>
-          <t>0.4260</t>
+          <t>0.426</t>
         </is>
       </c>
       <c r="AN8" s="2" t="inlineStr">
@@ -2249,7 +2247,7 @@
       </c>
       <c r="AO8" s="2" t="inlineStr">
         <is>
-          <t>0.8010</t>
+          <t>0.801</t>
         </is>
       </c>
       <c r="AP8" s="2" t="inlineStr">
@@ -2259,12 +2257,12 @@
       </c>
       <c r="AQ8" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AR8" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -2316,12 +2314,12 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>0.6730</t>
+          <t>0.673</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>0.8270</t>
+          <t>0.827</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -2336,42 +2334,42 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
@@ -2396,7 +2394,7 @@
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -2421,7 +2419,7 @@
       </c>
       <c r="AE9" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF9" s="3" t="inlineStr">
@@ -2446,7 +2444,7 @@
       </c>
       <c r="AJ9" s="3" t="inlineStr">
         <is>
-          <t>0.6280</t>
+          <t>0.628</t>
         </is>
       </c>
       <c r="AK9" s="3" t="inlineStr">
@@ -2466,7 +2464,7 @@
       </c>
       <c r="AN9" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO9" s="3" t="inlineStr">
@@ -2481,12 +2479,12 @@
       </c>
       <c r="AQ9" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2556,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -2568,17 +2566,17 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -2588,12 +2586,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -2603,12 +2601,12 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
@@ -2618,7 +2616,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -2628,12 +2626,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>0.1150</t>
+          <t>0.115</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
@@ -2653,17 +2651,17 @@
       </c>
       <c r="AG10" s="2" t="inlineStr">
         <is>
-          <t>0.0080</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="AH10" s="2" t="inlineStr">
         <is>
-          <t>0.0080</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="AI10" s="2" t="inlineStr">
         <is>
-          <t>0.7460</t>
+          <t>0.746</t>
         </is>
       </c>
       <c r="AJ10" s="2" t="inlineStr">
@@ -2703,12 +2701,12 @@
       </c>
       <c r="AQ10" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AR10" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2778,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -2790,17 +2788,17 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
@@ -2815,7 +2813,7 @@
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
@@ -2830,7 +2828,7 @@
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>0.0050</t>
+          <t>0.005</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
@@ -2840,7 +2838,7 @@
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA11" s="3" t="inlineStr">
@@ -2850,12 +2848,12 @@
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>0.2170</t>
+          <t>0.217</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>0.0050</t>
+          <t>0.005</t>
         </is>
       </c>
       <c r="AD11" s="3" t="inlineStr">
@@ -2865,7 +2863,7 @@
       </c>
       <c r="AE11" s="3" t="inlineStr">
         <is>
-          <t>0.0050</t>
+          <t>0.005</t>
         </is>
       </c>
       <c r="AF11" s="3" t="inlineStr">
@@ -2900,7 +2898,7 @@
       </c>
       <c r="AL11" s="3" t="inlineStr">
         <is>
-          <t>0.0150</t>
+          <t>0.015</t>
         </is>
       </c>
       <c r="AM11" s="3" t="inlineStr">
@@ -2910,7 +2908,7 @@
       </c>
       <c r="AN11" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO11" s="3" t="inlineStr">
@@ -2925,12 +2923,12 @@
       </c>
       <c r="AQ11" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -2957,7 +2955,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0.2430</t>
+          <t>0.243</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3002,27 +3000,27 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -3032,12 +3030,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -3047,7 +3045,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0.0280</t>
+          <t>0.028</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
@@ -3057,12 +3055,12 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>0.2150</t>
+          <t>0.215</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -3087,7 +3085,7 @@
       </c>
       <c r="AE12" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF12" s="2" t="inlineStr">
@@ -3107,7 +3105,7 @@
       </c>
       <c r="AI12" s="2" t="inlineStr">
         <is>
-          <t>0.5140</t>
+          <t>0.514</t>
         </is>
       </c>
       <c r="AJ12" s="2" t="inlineStr">
@@ -3122,7 +3120,7 @@
       </c>
       <c r="AL12" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AM12" s="2" t="inlineStr">
@@ -3137,7 +3135,7 @@
       </c>
       <c r="AO12" s="2" t="inlineStr">
         <is>
-          <t>0.7570</t>
+          <t>0.757</t>
         </is>
       </c>
       <c r="AP12" s="2" t="inlineStr">
@@ -3147,12 +3145,12 @@
       </c>
       <c r="AQ12" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AR12" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3222,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
@@ -3234,7 +3232,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>0.0020</t>
+          <t>0.002</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3244,7 +3242,7 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
@@ -3254,17 +3252,17 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t>0.8240</t>
+          <t>0.824</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
@@ -3284,7 +3282,7 @@
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -3369,7 +3367,7 @@
       </c>
       <c r="AQ13" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AR13" s="3" t="inlineStr">
@@ -3416,7 +3414,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0.8830</t>
+          <t>0.883</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3431,7 +3429,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0.8480</t>
+          <t>0.848</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -3441,12 +3439,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0.6140</t>
+          <t>0.614</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -3456,27 +3454,27 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3496,7 +3494,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
@@ -3506,7 +3504,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -3531,7 +3529,7 @@
       </c>
       <c r="AE14" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF14" s="2" t="inlineStr">
@@ -3591,12 +3589,12 @@
       </c>
       <c r="AQ14" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AR14" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -3668,27 +3666,27 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>0.1250</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
@@ -3698,12 +3696,12 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
@@ -3728,7 +3726,7 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -3753,7 +3751,7 @@
       </c>
       <c r="AE15" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF15" s="3" t="inlineStr">
@@ -3778,7 +3776,7 @@
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>0.5000</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="AK15" s="3" t="inlineStr">
@@ -3798,7 +3796,7 @@
       </c>
       <c r="AN15" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO15" s="3" t="inlineStr">
@@ -3813,12 +3811,12 @@
       </c>
       <c r="AQ15" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -3890,27 +3888,27 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0.0230</t>
+          <t>0.023</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -3920,7 +3918,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -3950,7 +3948,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -3975,7 +3973,7 @@
       </c>
       <c r="AE16" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF16" s="2" t="inlineStr">
@@ -3985,12 +3983,12 @@
       </c>
       <c r="AG16" s="2" t="inlineStr">
         <is>
-          <t>0.0920</t>
+          <t>0.092</t>
         </is>
       </c>
       <c r="AH16" s="2" t="inlineStr">
         <is>
-          <t>0.0920</t>
+          <t>0.092</t>
         </is>
       </c>
       <c r="AI16" s="2" t="inlineStr">
@@ -4020,7 +4018,7 @@
       </c>
       <c r="AN16" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO16" s="2" t="inlineStr">
@@ -4035,12 +4033,12 @@
       </c>
       <c r="AQ16" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AR16" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4070,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>0.5440</t>
+          <t>0.544</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -4112,17 +4110,17 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -4132,17 +4130,17 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
@@ -4152,7 +4150,7 @@
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
@@ -4172,7 +4170,7 @@
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -4182,7 +4180,7 @@
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
@@ -4197,7 +4195,7 @@
       </c>
       <c r="AE17" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF17" s="3" t="inlineStr">
@@ -4242,7 +4240,7 @@
       </c>
       <c r="AN17" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO17" s="3" t="inlineStr">
@@ -4257,12 +4255,12 @@
       </c>
       <c r="AQ17" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -4299,7 +4297,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1.0000</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -4334,7 +4332,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -4344,17 +4342,17 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -4364,12 +4362,12 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -4379,7 +4377,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
@@ -4389,17 +4387,17 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
@@ -4409,17 +4407,17 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>1.0000</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AE18" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF18" s="2" t="inlineStr">
@@ -4449,12 +4447,12 @@
       </c>
       <c r="AK18" s="2" t="inlineStr">
         <is>
-          <t>0.2500</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AL18" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AM18" s="2" t="inlineStr">
@@ -4464,7 +4462,7 @@
       </c>
       <c r="AN18" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO18" s="2" t="inlineStr">
@@ -4479,12 +4477,12 @@
       </c>
       <c r="AQ18" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AR18" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4519,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.0000</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -4556,7 +4554,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
@@ -4566,17 +4564,17 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
@@ -4586,17 +4584,17 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t>0.6140</t>
+          <t>0.614</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
@@ -4611,12 +4609,12 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>0.3070</t>
+          <t>0.307</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -4641,7 +4639,7 @@
       </c>
       <c r="AE19" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF19" s="3" t="inlineStr">
@@ -4686,7 +4684,7 @@
       </c>
       <c r="AN19" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO19" s="3" t="inlineStr">
@@ -4701,12 +4699,12 @@
       </c>
       <c r="AQ19" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -4778,27 +4776,27 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -4808,12 +4806,12 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -4828,7 +4826,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
@@ -4838,7 +4836,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -4863,7 +4861,7 @@
       </c>
       <c r="AE20" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF20" s="2" t="inlineStr">
@@ -4893,7 +4891,7 @@
       </c>
       <c r="AK20" s="2" t="inlineStr">
         <is>
-          <t>0.7500</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AL20" s="2" t="inlineStr">
@@ -4908,7 +4906,7 @@
       </c>
       <c r="AN20" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO20" s="2" t="inlineStr">
@@ -4923,12 +4921,12 @@
       </c>
       <c r="AQ20" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AR20" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4978,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>0.6800</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
@@ -5020,7 +5018,7 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
@@ -5030,12 +5028,12 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
@@ -5060,12 +5058,12 @@
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>0.0730</t>
+          <t>0.073</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
@@ -5085,7 +5083,7 @@
       </c>
       <c r="AE21" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF21" s="3" t="inlineStr">
@@ -5130,7 +5128,7 @@
       </c>
       <c r="AN21" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO21" s="3" t="inlineStr">
@@ -5140,7 +5138,7 @@
       </c>
       <c r="AP21" s="3" t="inlineStr">
         <is>
-          <t>0.6010</t>
+          <t>0.601</t>
         </is>
       </c>
       <c r="AQ21" s="3" t="inlineStr">
@@ -5150,7 +5148,7 @@
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5220,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -5242,7 +5240,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -5252,12 +5250,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -5282,12 +5280,12 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
@@ -5307,7 +5305,7 @@
       </c>
       <c r="AE22" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF22" s="2" t="inlineStr">
@@ -5342,7 +5340,7 @@
       </c>
       <c r="AL22" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AM22" s="2" t="inlineStr">
@@ -5352,7 +5350,7 @@
       </c>
       <c r="AN22" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO22" s="2" t="inlineStr">
@@ -5367,12 +5365,12 @@
       </c>
       <c r="AQ22" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AR22" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -5444,27 +5442,27 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
@@ -5474,22 +5472,22 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t>0.6410</t>
+          <t>0.641</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>0.1410</t>
+          <t>0.141</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
@@ -5504,7 +5502,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -5529,7 +5527,7 @@
       </c>
       <c r="AE23" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF23" s="3" t="inlineStr">
@@ -5564,7 +5562,7 @@
       </c>
       <c r="AL23" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AM23" s="3" t="inlineStr">
@@ -5574,12 +5572,12 @@
       </c>
       <c r="AN23" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
-          <t>0.8590</t>
+          <t>0.859</t>
         </is>
       </c>
       <c r="AP23" s="3" t="inlineStr">
@@ -5594,7 +5592,7 @@
       </c>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5664,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -5681,12 +5679,12 @@
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
@@ -5696,7 +5694,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -5716,7 +5714,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
@@ -5726,12 +5724,12 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0.1930</t>
+          <t>0.193</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
@@ -5751,7 +5749,7 @@
       </c>
       <c r="AE24" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF24" s="2" t="inlineStr">
@@ -5796,7 +5794,7 @@
       </c>
       <c r="AN24" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO24" s="2" t="inlineStr">
@@ -5811,12 +5809,12 @@
       </c>
       <c r="AQ24" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AR24" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -5843,7 +5841,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>0.0680</t>
+          <t>0.068</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -5888,7 +5886,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
@@ -5898,32 +5896,32 @@
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
@@ -5948,7 +5946,7 @@
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -5973,7 +5971,7 @@
       </c>
       <c r="AE25" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF25" s="3" t="inlineStr">
@@ -5983,12 +5981,12 @@
       </c>
       <c r="AG25" s="3" t="inlineStr">
         <is>
-          <t>0.0680</t>
+          <t>0.068</t>
         </is>
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>0.0680</t>
+          <t>0.068</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
@@ -6008,7 +6006,7 @@
       </c>
       <c r="AL25" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AM25" s="3" t="inlineStr">
@@ -6018,7 +6016,7 @@
       </c>
       <c r="AN25" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO25" s="3" t="inlineStr">
@@ -6033,12 +6031,12 @@
       </c>
       <c r="AQ25" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -6110,12 +6108,12 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6130,7 +6128,7 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
@@ -6140,7 +6138,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6155,7 +6153,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
@@ -6170,7 +6168,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -6195,7 +6193,7 @@
       </c>
       <c r="AE26" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF26" s="2" t="inlineStr">
@@ -6255,12 +6253,12 @@
       </c>
       <c r="AQ26" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AR26" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6280,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>0.2440</t>
+          <t>0.244</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -6332,7 +6330,7 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
@@ -6347,12 +6345,12 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>0.0060</t>
+          <t>0.006</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
@@ -6362,17 +6360,17 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t>0.6190</t>
+          <t>0.619</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
@@ -6392,7 +6390,7 @@
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -6417,7 +6415,7 @@
       </c>
       <c r="AE27" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF27" s="3" t="inlineStr">
@@ -6452,7 +6450,7 @@
       </c>
       <c r="AL27" s="3" t="inlineStr">
         <is>
-          <t>0.0060</t>
+          <t>0.006</t>
         </is>
       </c>
       <c r="AM27" s="3" t="inlineStr">
@@ -6462,7 +6460,7 @@
       </c>
       <c r="AN27" s="3" t="inlineStr">
         <is>
-          <t>0.0060</t>
+          <t>0.006</t>
         </is>
       </c>
       <c r="AO27" s="3" t="inlineStr">
@@ -6472,17 +6470,17 @@
       </c>
       <c r="AP27" s="3" t="inlineStr">
         <is>
-          <t>0.1310</t>
+          <t>0.131</t>
         </is>
       </c>
       <c r="AQ27" s="3" t="inlineStr">
         <is>
-          <t>0.0060</t>
+          <t>0.006</t>
         </is>
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -6509,7 +6507,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0.2110</t>
+          <t>0.211</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -6554,12 +6552,12 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0.0050</t>
+          <t>0.005</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -6584,7 +6582,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6599,7 +6597,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0.1560</t>
+          <t>0.156</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
@@ -6634,12 +6632,12 @@
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>0.8690</t>
+          <t>0.869</t>
         </is>
       </c>
       <c r="AE28" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF28" s="2" t="inlineStr">
@@ -6694,7 +6692,7 @@
       </c>
       <c r="AP28" s="2" t="inlineStr">
         <is>
-          <t>0.5220</t>
+          <t>0.522</t>
         </is>
       </c>
       <c r="AQ28" s="2" t="inlineStr">
@@ -6704,7 +6702,7 @@
       </c>
       <c r="AR28" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -6741,7 +6739,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>0.9420</t>
+          <t>0.942</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -6771,42 +6769,42 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>0.0870</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>0.0290</t>
+          <t>0.029</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>0.0290</t>
+          <t>0.029</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
@@ -6831,17 +6829,17 @@
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>0.0870</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>0.0580</t>
+          <t>0.058</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
@@ -6861,7 +6859,7 @@
       </c>
       <c r="AE29" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF29" s="3" t="inlineStr">
@@ -6916,17 +6914,17 @@
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>0.5580</t>
+          <t>0.558</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6996,7 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -7008,32 +7006,32 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -7048,17 +7046,17 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -7083,7 +7081,7 @@
       </c>
       <c r="AE30" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF30" s="2" t="inlineStr">
@@ -7118,7 +7116,7 @@
       </c>
       <c r="AL30" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AM30" s="2" t="inlineStr">
@@ -7128,7 +7126,7 @@
       </c>
       <c r="AN30" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO30" s="2" t="inlineStr">
@@ -7143,12 +7141,12 @@
       </c>
       <c r="AQ30" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AR30" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -7215,47 +7213,47 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
@@ -7265,12 +7263,12 @@
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
@@ -7280,12 +7278,12 @@
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
@@ -7300,12 +7298,12 @@
       </c>
       <c r="AD31" s="3" t="inlineStr">
         <is>
-          <t>1.0000</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AE31" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF31" s="3" t="inlineStr">
@@ -7325,12 +7323,12 @@
       </c>
       <c r="AI31" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AK31" s="3" t="inlineStr">
@@ -7340,17 +7338,17 @@
       </c>
       <c r="AL31" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AM31" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AN31" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO31" s="3" t="inlineStr">
@@ -7365,12 +7363,12 @@
       </c>
       <c r="AQ31" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -7397,7 +7395,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0.1250</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -7432,7 +7430,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>0.6250</t>
+          <t>0.625</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -7442,7 +7440,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -7452,42 +7450,42 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0.6250</t>
+          <t>0.625</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
@@ -7502,7 +7500,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -7527,7 +7525,7 @@
       </c>
       <c r="AE32" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF32" s="2" t="inlineStr">
@@ -7562,7 +7560,7 @@
       </c>
       <c r="AL32" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AM32" s="2" t="inlineStr">
@@ -7572,7 +7570,7 @@
       </c>
       <c r="AN32" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO32" s="2" t="inlineStr">
@@ -7587,165 +7585,169 @@
       </c>
       <c r="AQ32" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AR32" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr"/>
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>562</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>9.4511</t>
+          <t>6.4609</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>0.2065</t>
+          <t>0.2242</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>0.2772</t>
+          <t>0.0783</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>0.3043</t>
+          <t>0.2171</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>0.9293</t>
+          <t>0.927</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>0.5815</t>
+          <t>0.4484</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>0.0598</t>
+          <t>0.0943</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>0.5326</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>0.4185</t>
+          <t>0.3701</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>0.5272</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>0.3696</t>
+          <t>0.1655</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>0.0652</t>
+          <t>0.0178</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>0.0109</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.0302</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t>0.0109</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t>0.4620</t>
+          <t>0.2776</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>0.0543</t>
+          <t>0.0854</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>0.0380</t>
+          <t>0.0338</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>0.2446</t>
+          <t>0.1477</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>0.1685</t>
+          <t>0.0142</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.048</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>0.1630</t>
+          <t>0.1388</t>
         </is>
       </c>
       <c r="AD33" s="3" t="inlineStr">
         <is>
-          <t>0.7065</t>
+          <t>0.5178</t>
         </is>
       </c>
       <c r="AE33" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF33" s="3" t="inlineStr">
@@ -7755,219 +7757,219 @@
       </c>
       <c r="AG33" s="3" t="inlineStr">
         <is>
-          <t>0.0978</t>
+          <t>0.1085</t>
         </is>
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.1014</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
         <is>
-          <t>0.4130</t>
+          <t>0.1904</t>
         </is>
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>0.4239</t>
+          <t>0.1957</t>
         </is>
       </c>
       <c r="AK33" s="3" t="inlineStr">
         <is>
-          <t>0.6413</t>
+          <t>0.4769</t>
         </is>
       </c>
       <c r="AL33" s="3" t="inlineStr">
         <is>
-          <t>0.0163</t>
+          <t>0.0071</t>
         </is>
       </c>
       <c r="AM33" s="3" t="inlineStr">
         <is>
-          <t>0.3641</t>
+          <t>0.2633</t>
         </is>
       </c>
       <c r="AN33" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0018</t>
         </is>
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
-          <t>0.6250</t>
+          <t>0.4555</t>
         </is>
       </c>
       <c r="AP33" s="3" t="inlineStr">
         <is>
-          <t>0.4674</t>
+          <t>0.2438</t>
         </is>
       </c>
       <c r="AQ33" s="3" t="inlineStr">
         <is>
-          <t>0.0109</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>0.0054</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>77</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>6.4609</t>
+          <t>5.1818</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>0.2242</t>
+          <t>0.2597</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>0.0783</t>
+          <t>0.2208</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>0.2171</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0.9270</t>
+          <t>0.8701</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0.4484</t>
+          <t>0.2468</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0.0943</t>
+          <t>0.0909</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>0.2900</t>
+          <t>0.2597</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0.3701</t>
+          <t>0.2468</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>0.2900</t>
+          <t>0.2597</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0.1655</t>
+          <t>0.039</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0.0178</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>0.0302</t>
+          <t>0.1299</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0.2776</t>
+          <t>0.3247</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0.0854</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>0.0338</t>
+          <t>0.0519</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>0.1477</t>
+          <t>0.2078</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>0.0142</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>0.0480</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>0.1388</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>0.5178</t>
+          <t>0.4286</t>
         </is>
       </c>
       <c r="AE34" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF34" s="2" t="inlineStr">
@@ -7977,219 +7979,219 @@
       </c>
       <c r="AG34" s="2" t="inlineStr">
         <is>
-          <t>0.1085</t>
+          <t>0.0909</t>
         </is>
       </c>
       <c r="AH34" s="2" t="inlineStr">
         <is>
-          <t>0.1014</t>
+          <t>0.0909</t>
         </is>
       </c>
       <c r="AI34" s="2" t="inlineStr">
         <is>
-          <t>0.1904</t>
+          <t>0.1688</t>
         </is>
       </c>
       <c r="AJ34" s="2" t="inlineStr">
         <is>
-          <t>0.1957</t>
+          <t>0.1688</t>
         </is>
       </c>
       <c r="AK34" s="2" t="inlineStr">
         <is>
-          <t>0.4769</t>
+          <t>0.4286</t>
         </is>
       </c>
       <c r="AL34" s="2" t="inlineStr">
         <is>
-          <t>0.0071</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AM34" s="2" t="inlineStr">
         <is>
-          <t>0.2633</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AN34" s="2" t="inlineStr">
         <is>
-          <t>0.0018</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO34" s="2" t="inlineStr">
         <is>
-          <t>0.4555</t>
+          <t>0.4935</t>
         </is>
       </c>
       <c r="AP34" s="2" t="inlineStr">
         <is>
-          <t>0.2438</t>
+          <t>0.0649</t>
         </is>
       </c>
       <c r="AQ34" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.039</t>
         </is>
       </c>
       <c r="AR34" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>574</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>5.1818</t>
+          <t>5.1307</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>0.2597</t>
+          <t>0.216</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>0.2208</t>
+          <t>0.1568</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.122</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>0.8701</t>
+          <t>0.8171</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>0.2468</t>
+          <t>0.2718</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>0.0909</t>
+          <t>0.0523</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>0.2597</t>
+          <t>0.3118</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>0.2468</t>
+          <t>0.223</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>0.2597</t>
+          <t>0.3118</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>0.0390</t>
+          <t>0.0854</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0139</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0052</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t>0.1299</t>
+          <t>0.0418</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t>0.3247</t>
+          <t>0.2422</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0436</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>0.0519</t>
+          <t>0.0105</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t>0.2078</t>
+          <t>0.1429</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0052</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0296</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0366</t>
         </is>
       </c>
       <c r="AD35" s="3" t="inlineStr">
         <is>
-          <t>0.4286</t>
+          <t>0.4111</t>
         </is>
       </c>
       <c r="AE35" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF35" s="3" t="inlineStr">
@@ -8199,219 +8201,219 @@
       </c>
       <c r="AG35" s="3" t="inlineStr">
         <is>
-          <t>0.0909</t>
+          <t>0.1045</t>
         </is>
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>0.0909</t>
+          <t>0.1045</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
         <is>
-          <t>0.1688</t>
+          <t>0.0976</t>
         </is>
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>0.1688</t>
+          <t>0.0976</t>
         </is>
       </c>
       <c r="AK35" s="3" t="inlineStr">
         <is>
-          <t>0.4286</t>
+          <t>0.4024</t>
         </is>
       </c>
       <c r="AL35" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0035</t>
         </is>
       </c>
       <c r="AM35" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.1481</t>
         </is>
       </c>
       <c r="AN35" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
-          <t>0.4935</t>
+          <t>0.3275</t>
         </is>
       </c>
       <c r="AP35" s="3" t="inlineStr">
         <is>
-          <t>0.0649</t>
+          <t>0.2944</t>
         </is>
       </c>
       <c r="AQ35" s="3" t="inlineStr">
         <is>
-          <t>0.0390</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>5.1307</t>
+          <t>4.3519</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>0.2160</t>
+          <t>0.1667</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0.1568</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>0.1220</t>
+          <t>0.1667</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0.8171</t>
+          <t>0.8519</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0.2718</t>
+          <t>0.4444</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0.0523</t>
+          <t>0.1296</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>0.3118</t>
+          <t>0.1852</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0.2230</t>
+          <t>0.2778</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>0.3118</t>
+          <t>0.1852</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0.0854</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0.0139</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0.0052</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>0.0418</t>
+          <t>0.037</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0.2422</t>
+          <t>0.037</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0.0436</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>0.0105</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>0.1429</t>
+          <t>0.1481</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>0.0052</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>0.0296</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>0.0366</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>0.4111</t>
+          <t>0.3333</t>
         </is>
       </c>
       <c r="AE36" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AF36" s="2" t="inlineStr">
@@ -8421,219 +8423,219 @@
       </c>
       <c r="AG36" s="2" t="inlineStr">
         <is>
-          <t>0.1045</t>
+          <t>0.1852</t>
         </is>
       </c>
       <c r="AH36" s="2" t="inlineStr">
         <is>
-          <t>0.1045</t>
+          <t>0.1852</t>
         </is>
       </c>
       <c r="AI36" s="2" t="inlineStr">
         <is>
-          <t>0.0976</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AJ36" s="2" t="inlineStr">
         <is>
-          <t>0.0976</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AK36" s="2" t="inlineStr">
         <is>
-          <t>0.4024</t>
+          <t>0.2593</t>
         </is>
       </c>
       <c r="AL36" s="2" t="inlineStr">
         <is>
-          <t>0.0035</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AM36" s="2" t="inlineStr">
         <is>
-          <t>0.1481</t>
+          <t>0.1667</t>
         </is>
       </c>
       <c r="AN36" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO36" s="2" t="inlineStr">
         <is>
-          <t>0.3275</t>
+          <t>0.3148</t>
         </is>
       </c>
       <c r="AP36" s="2" t="inlineStr">
         <is>
-          <t>0.2944</t>
+          <t>0.1296</t>
         </is>
       </c>
       <c r="AQ36" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AR36" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>4.3519</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>0.1667</t>
+          <t>0.025</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0625</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>0.1667</t>
+          <t>0.0625</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>0.8519</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>0.4444</t>
+          <t>0.325</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>0.1296</t>
+          <t>0.025</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>0.1852</t>
+          <t>0.175</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>0.2778</t>
+          <t>0.0625</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>0.1852</t>
+          <t>0.175</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.1375</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t>0.0370</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t>0.0370</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0125</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.025</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>0.1481</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0625</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AD37" s="3" t="inlineStr">
         <is>
-          <t>0.3333</t>
+          <t>0.2375</t>
         </is>
       </c>
       <c r="AE37" s="3" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF37" s="3" t="inlineStr">
@@ -8643,219 +8645,219 @@
       </c>
       <c r="AG37" s="3" t="inlineStr">
         <is>
-          <t>0.1852</t>
+          <t>0.0125</t>
         </is>
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>0.1852</t>
+          <t>0.0125</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.1625</t>
         </is>
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.1625</t>
         </is>
       </c>
       <c r="AK37" s="3" t="inlineStr">
         <is>
-          <t>0.2593</t>
+          <t>0.1875</t>
         </is>
       </c>
       <c r="AL37" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AM37" s="3" t="inlineStr">
         <is>
-          <t>0.1667</t>
+          <t>0.0625</t>
         </is>
       </c>
       <c r="AN37" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
-          <t>0.3148</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="AP37" s="3" t="inlineStr">
         <is>
-          <t>0.1296</t>
+          <t>0.1375</t>
         </is>
       </c>
       <c r="AQ37" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>234</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>3.2000</t>
+          <t>2.0641</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>0.0250</t>
+          <t>0.0427</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>0.0625</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>0.0625</t>
+          <t>0.0043</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>0.7500</t>
+          <t>0.7863</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0.3250</t>
+          <t>0.2821</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>0.0250</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>0.1750</t>
+          <t>0.0855</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0.0625</t>
+          <t>0.0641</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>0.1750</t>
+          <t>0.0855</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0.1375</t>
+          <t>0.0214</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0043</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0.0750</t>
+          <t>0.0427</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>0.0125</t>
+          <t>0.0342</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>0.0250</t>
+          <t>0.0085</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>0.0750</t>
+          <t>0.0427</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>0.0625</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>0.0500</t>
+          <t>0.0256</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>0.2375</t>
+          <t>0.0897</t>
         </is>
       </c>
       <c r="AE38" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF38" s="2" t="inlineStr">
@@ -8865,284 +8867,62 @@
       </c>
       <c r="AG38" s="2" t="inlineStr">
         <is>
-          <t>0.0125</t>
+          <t>0.0427</t>
         </is>
       </c>
       <c r="AH38" s="2" t="inlineStr">
         <is>
-          <t>0.0125</t>
+          <t>0.0427</t>
         </is>
       </c>
       <c r="AI38" s="2" t="inlineStr">
         <is>
-          <t>0.1625</t>
+          <t>0.0214</t>
         </is>
       </c>
       <c r="AJ38" s="2" t="inlineStr">
         <is>
-          <t>0.1625</t>
+          <t>0.0214</t>
         </is>
       </c>
       <c r="AK38" s="2" t="inlineStr">
         <is>
-          <t>0.1875</t>
+          <t>0.0897</t>
         </is>
       </c>
       <c r="AL38" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0214</t>
         </is>
       </c>
       <c r="AM38" s="2" t="inlineStr">
         <is>
-          <t>0.0625</t>
+          <t>0.0385</t>
         </is>
       </c>
       <c r="AN38" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO38" s="2" t="inlineStr">
         <is>
-          <t>0.1250</t>
+          <t>0.0812</t>
         </is>
       </c>
       <c r="AP38" s="2" t="inlineStr">
         <is>
-          <t>0.1375</t>
+          <t>0.0855</t>
         </is>
       </c>
       <c r="AQ38" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AR38" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>2.0641</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>0.0427</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>0.0000</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>0.0043</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>0.7863</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>0.2821</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>0.0000</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>0.0855</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>0.0641</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t>0.0855</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t>0.0214</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t>0.0000</t>
-        </is>
-      </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>0.0000</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="inlineStr">
-        <is>
-          <t>0.0000</t>
-        </is>
-      </c>
-      <c r="Q39" s="3" t="inlineStr">
-        <is>
-          <t>0.0000</t>
-        </is>
-      </c>
-      <c r="R39" s="3" t="inlineStr">
-        <is>
-          <t>0.0000</t>
-        </is>
-      </c>
-      <c r="S39" s="3" t="inlineStr">
-        <is>
-          <t>0.0043</t>
-        </is>
-      </c>
-      <c r="T39" s="3" t="inlineStr">
-        <is>
-          <t>0.0000</t>
-        </is>
-      </c>
-      <c r="U39" s="3" t="inlineStr">
-        <is>
-          <t>0.0000</t>
-        </is>
-      </c>
-      <c r="V39" s="3" t="inlineStr">
-        <is>
-          <t>0.0427</t>
-        </is>
-      </c>
-      <c r="W39" s="3" t="inlineStr">
-        <is>
-          <t>0.0342</t>
-        </is>
-      </c>
-      <c r="X39" s="3" t="inlineStr">
-        <is>
-          <t>0.0085</t>
-        </is>
-      </c>
-      <c r="Y39" s="3" t="inlineStr">
-        <is>
-          <t>0.0427</t>
-        </is>
-      </c>
-      <c r="Z39" s="3" t="inlineStr">
-        <is>
-          <t>0.0000</t>
-        </is>
-      </c>
-      <c r="AA39" s="3" t="inlineStr">
-        <is>
-          <t>0.0000</t>
-        </is>
-      </c>
-      <c r="AB39" s="3" t="inlineStr">
-        <is>
-          <t>0.0000</t>
-        </is>
-      </c>
-      <c r="AC39" s="3" t="inlineStr">
-        <is>
-          <t>0.0256</t>
-        </is>
-      </c>
-      <c r="AD39" s="3" t="inlineStr">
-        <is>
-          <t>0.0897</t>
-        </is>
-      </c>
-      <c r="AE39" s="3" t="inlineStr">
-        <is>
-          <t>0.0000</t>
-        </is>
-      </c>
-      <c r="AF39" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG39" s="3" t="inlineStr">
-        <is>
-          <t>0.0427</t>
-        </is>
-      </c>
-      <c r="AH39" s="3" t="inlineStr">
-        <is>
-          <t>0.0427</t>
-        </is>
-      </c>
-      <c r="AI39" s="3" t="inlineStr">
-        <is>
-          <t>0.0214</t>
-        </is>
-      </c>
-      <c r="AJ39" s="3" t="inlineStr">
-        <is>
-          <t>0.0214</t>
-        </is>
-      </c>
-      <c r="AK39" s="3" t="inlineStr">
-        <is>
-          <t>0.0897</t>
-        </is>
-      </c>
-      <c r="AL39" s="3" t="inlineStr">
-        <is>
-          <t>0.0214</t>
-        </is>
-      </c>
-      <c r="AM39" s="3" t="inlineStr">
-        <is>
-          <t>0.0385</t>
-        </is>
-      </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>0.0000</t>
-        </is>
-      </c>
-      <c r="AO39" s="3" t="inlineStr">
-        <is>
-          <t>0.0812</t>
-        </is>
-      </c>
-      <c r="AP39" s="3" t="inlineStr">
-        <is>
-          <t>0.0855</t>
-        </is>
-      </c>
-      <c r="AQ39" s="3" t="inlineStr">
-        <is>
-          <t>0.0000</t>
-        </is>
-      </c>
-      <c r="AR39" s="3" t="inlineStr">
-        <is>
-          <t>0.0000</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
